--- a/service_providers/service_providers_list_ep.xlsx
+++ b/service_providers/service_providers_list_ep.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wopi.dropbox.com/wopi/files/oid_7921831851251265536/WOPIServiceId_TP_DROPBOX_PLUS/WOPIUserId_-/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="8_{FF53A251-D3D9-461B-B593-C5824D5A253F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2685076-8FBF-46A6-9654-320770490364}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{FF53A251-D3D9-461B-B593-C5824D5A253F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7E0E707-5D0D-4263-AF13-847BB6DEE74B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CF8A48F4-BB4D-4102-AF50-A54BBE298DBA}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{CF8A48F4-BB4D-4102-AF50-A54BBE298DBA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="39">
   <si>
     <t>name</t>
   </si>
@@ -129,9 +129,6 @@
   </si>
   <si>
     <t>https://www.tabithacantucounseling.com/</t>
-  </si>
-  <si>
-    <t>I am a virtual private practice serving women &amp; teen girls 13+</t>
   </si>
   <si>
     <t>To families affected by drunk driving, my heart is with you. Even in the midst of hardship and loss, help is always available to support you.</t>
@@ -853,7 +850,7 @@
         <v>14</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>15</v>
@@ -888,7 +885,7 @@
         <v>21</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>22</v>
@@ -932,15 +929,15 @@
         <v>29</v>
       </c>
       <c r="H4" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" s="14" t="s">
         <v>30</v>
-      </c>
-      <c r="I4" s="14" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="115.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>12</v>
@@ -949,20 +946,20 @@
         <v>20</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5" s="17"/>
       <c r="F5" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H5" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="19" t="s">
         <v>34</v>
-      </c>
-      <c r="I5" s="19" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/service_providers/service_providers_list_ep.xlsx
+++ b/service_providers/service_providers_list_ep.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wopi.dropbox.com/wopi/files/oid_7921831851251265536/WOPIServiceId_TP_DROPBOX_PLUS/WOPIUserId_-/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{FF53A251-D3D9-461B-B593-C5824D5A253F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7E0E707-5D0D-4263-AF13-847BB6DEE74B}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="8_{FF53A251-D3D9-461B-B593-C5824D5A253F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F2CF227-8996-4423-933F-74B6F36228AE}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{CF8A48F4-BB4D-4102-AF50-A54BBE298DBA}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="53">
   <si>
     <t>name</t>
   </si>
@@ -60,9 +60,6 @@
   </si>
   <si>
     <t>contact_preference</t>
-  </si>
-  <si>
-    <t>email</t>
   </si>
   <si>
     <t>website</t>
@@ -157,6 +154,51 @@
   </si>
   <si>
     <t>v.reyna@risingperspectivecounseling.com</t>
+  </si>
+  <si>
+    <t>Children's Grief Center El Paso</t>
+  </si>
+  <si>
+    <t>Phone, Email</t>
+  </si>
+  <si>
+    <t>915-532-6004</t>
+  </si>
+  <si>
+    <t>2616 Montana Ave., El Paso, TX, 79903</t>
+  </si>
+  <si>
+    <t>Our mission at CGC is to provide a safe, welcoming space for your family to find hope and begin healing after this unimaginable loss. Our main services include individual grief therapy as well as peer-led grief support groups. There is no rush and no timeline; we just want you to know that our doors are open, whenever you're ready.</t>
+  </si>
+  <si>
+    <t>www.cgcelpaso.org</t>
+  </si>
+  <si>
+    <t>Counseling/Mental health support, Support groups, Grief counseling</t>
+  </si>
+  <si>
+    <t>email_1</t>
+  </si>
+  <si>
+    <t>email_1_description</t>
+  </si>
+  <si>
+    <t>email_2</t>
+  </si>
+  <si>
+    <t>email_2_description</t>
+  </si>
+  <si>
+    <t>General questions</t>
+  </si>
+  <si>
+    <t>frontdesk@cgcelpaso.org</t>
+  </si>
+  <si>
+    <t>Programming or scheduling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">luisa@cgcelpaso.org </t>
   </si>
 </sst>
 </file>
@@ -215,7 +257,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -382,6 +424,51 @@
       </right>
       <top style="medium">
         <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="medium">
         <color rgb="FF442F65"/>
@@ -393,7 +480,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -450,6 +537,18 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -787,7 +886,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98EDC8CC-1C43-4704-8ECE-5759E54530CE}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr defaultColWidth="45.25" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.5" bestFit="1" customWidth="1"/>
@@ -795,13 +894,15 @@
     <col min="3" max="3" width="25.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.75" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="32.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="44.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="32.125" customWidth="1"/>
+    <col min="10" max="10" width="32.125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="44.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -818,159 +919,227 @@
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="M1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="77.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>4</v>
+      <c r="B2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2">
+        <v>31.7637</v>
+      </c>
+      <c r="N2">
+        <v>-106.31100000000001</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="77.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="3" spans="1:14" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2">
-        <v>31.7637</v>
-      </c>
-      <c r="K2">
-        <v>-106.31100000000001</v>
+      <c r="C3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3">
+        <v>31.7486</v>
+      </c>
+      <c r="N3">
+        <v>-106.2927</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+    <row r="4" spans="1:14" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="7" t="s">
+      <c r="D4" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3">
-        <v>31.7486</v>
-      </c>
-      <c r="K3">
-        <v>-106.2927</v>
+      <c r="E4" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="14" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" s="14" t="s">
+    <row r="5" spans="1:14" ht="115.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="115.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="B5" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="16" t="s">
         <v>31</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>32</v>
       </c>
       <c r="E5" s="17"/>
       <c r="F5" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="77.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="19" t="s">
-        <v>34</v>
+      <c r="B6" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J6" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="L6" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="M6">
+        <v>31.780988113293802</v>
+      </c>
+      <c r="N6">
+        <v>-106.46459054575099</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="http://www.epmobilenotarypublic.com/" xr:uid="{C7AF46B5-9205-4C9B-B55B-02DB6EAFA028}"/>
-    <hyperlink ref="G3" r:id="rId2" display="http://www.mindforwardhealthcenter.com/" xr:uid="{5A4EA41D-5D25-4908-BB67-792DC513BADB}"/>
-    <hyperlink ref="G4" r:id="rId3" xr:uid="{82A5C6CB-28AC-497D-9858-0AAFCCA85004}"/>
-    <hyperlink ref="G5" r:id="rId4" xr:uid="{37C2BABF-6621-4809-8DB3-2BF69F67CE98}"/>
+    <hyperlink ref="J2" r:id="rId1" display="http://www.epmobilenotarypublic.com/" xr:uid="{C7AF46B5-9205-4C9B-B55B-02DB6EAFA028}"/>
+    <hyperlink ref="J3" r:id="rId2" display="http://www.mindforwardhealthcenter.com/" xr:uid="{5A4EA41D-5D25-4908-BB67-792DC513BADB}"/>
+    <hyperlink ref="J4" r:id="rId3" xr:uid="{82A5C6CB-28AC-497D-9858-0AAFCCA85004}"/>
+    <hyperlink ref="J5" r:id="rId4" xr:uid="{37C2BABF-6621-4809-8DB3-2BF69F67CE98}"/>
     <hyperlink ref="F5" r:id="rId5" xr:uid="{8DEE1142-839F-47E3-8008-BCCE1BF72F70}"/>
+    <hyperlink ref="J6" r:id="rId6" xr:uid="{62AF5E62-16BC-49CC-AEA8-F705FC017B64}"/>
+    <hyperlink ref="F6" r:id="rId7" xr:uid="{9D15480B-B931-4A7B-A609-1B90E97C191D}"/>
+    <hyperlink ref="H6" r:id="rId8" xr:uid="{ADDB6F17-12D4-499C-89AA-55883824517B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId6"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId9"/>
 </worksheet>
 </file>